--- a/docs/103_RIME對照工具【拼音帶調號】.xlsx
+++ b/docs/103_RIME對照工具【拼音帶調號】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DE62CE-21EB-4037-B779-A9B941DE365F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378616CC-F980-47A2-921A-8368688550B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1ECF7FA8-0673-4BE6-8306-9C5F7A600CEF}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{1ECF7FA8-0673-4BE6-8306-9C5F7A600CEF}"/>
   </bookViews>
   <sheets>
     <sheet name="【調】韻母標調" sheetId="1" r:id="rId1"/>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="J8" s="10" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D8,4)))), "")</f>
+        <f t="shared" ref="J8:J13" si="5">IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D8,4)))), "")</f>
         <v>ô͘</v>
       </c>
       <c r="K8" s="10" t="str">
@@ -2821,7 +2821,7 @@
         <v>6</v>
       </c>
       <c r="J9" s="10" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D9,4)))), "")</f>
+        <f t="shared" si="5"/>
         <v>ó͘</v>
       </c>
       <c r="K9" s="10" t="str">
@@ -2881,7 +2881,7 @@
         <v>7</v>
       </c>
       <c r="J10" s="10" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D10,4)))), "")</f>
+        <f t="shared" si="5"/>
         <v>ō͘</v>
       </c>
       <c r="K10" s="10" t="str">
@@ -2941,7 +2941,7 @@
         <v>8</v>
       </c>
       <c r="J11" s="10" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D11,4)))), "")</f>
+        <f t="shared" si="5"/>
         <v>o̍͘</v>
       </c>
       <c r="K11" s="10" t="str">
@@ -2994,7 +2994,7 @@
         <v>9</v>
       </c>
       <c r="J12" s="10" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D12,4)))), "")</f>
+        <f t="shared" si="5"/>
         <v>ő͘</v>
       </c>
       <c r="K12" s="10" t="str">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="10" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(D13,4)))), "")</f>
+        <f t="shared" si="5"/>
         <v>o̊͘</v>
       </c>
       <c r="K13" s="10" t="str">
@@ -3161,23 +3161,23 @@
         <v xml:space="preserve">    - xform/a1/a/</v>
       </c>
       <c r="W16" t="str">
-        <f t="shared" ref="W16:AA22" si="5" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, L$15, "/",L16,"/")</f>
+        <f t="shared" ref="W16:AA22" si="6" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, L$15, "/",L16,"/")</f>
         <v xml:space="preserve">    - xform/a2/á/</v>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/a3/à/</v>
       </c>
       <c r="Y16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/a4/a/</v>
       </c>
       <c r="Z16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/a5/â/</v>
       </c>
       <c r="AA16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/a6/á/</v>
       </c>
       <c r="AB16" t="str">
@@ -3185,15 +3185,15 @@
         <v xml:space="preserve">    - xform/a7/ā/</v>
       </c>
       <c r="AC16" t="str">
-        <f t="shared" ref="AC16:AC22" si="6" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, R$15, "/",R16,"/")</f>
+        <f t="shared" ref="AC16:AC22" si="7" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, R$15, "/",R16,"/")</f>
         <v xml:space="preserve">    - xform/a8/a̍/</v>
       </c>
       <c r="AD16" t="str">
-        <f t="shared" ref="AD16:AD22" si="7" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, S$15, "/",S16,"/")</f>
+        <f t="shared" ref="AD16:AD22" si="8" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, S$15, "/",S16,"/")</f>
         <v xml:space="preserve">    - xform/a9/a̋/</v>
       </c>
       <c r="AE16" t="str">
-        <f t="shared" ref="AE16:AE22" si="8" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, T$15, "/",T16,"/")</f>
+        <f t="shared" ref="AE16:AE22" si="9" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J16, T$15, "/",T16,"/")</f>
         <v xml:space="preserve">    - xform/a0/å/</v>
       </c>
     </row>
@@ -3242,43 +3242,43 @@
         <v>i̊</v>
       </c>
       <c r="V17" t="str">
-        <f t="shared" ref="V17:V22" si="9" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J17, K$15, "/",K17,"/")</f>
+        <f t="shared" ref="V17:V22" si="10" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J17, K$15, "/",K17,"/")</f>
         <v xml:space="preserve">    - xform/i1/i/</v>
       </c>
       <c r="W17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/i2/í/</v>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/i3/ì/</v>
       </c>
       <c r="Y17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/i4/i/</v>
       </c>
       <c r="Z17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/i5/î/</v>
       </c>
       <c r="AA17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve">    - xform/i6/í/</v>
       </c>
       <c r="AB17" t="str">
-        <f t="shared" ref="AB17:AB22" si="10" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J17, Q$15, "/",Q17,"/")</f>
+        <f t="shared" ref="AB17:AB22" si="11" xml:space="preserve"> _xlfn.CONCAT("    - xform/", $J17, Q$15, "/",Q17,"/")</f>
         <v xml:space="preserve">    - xform/i7/ī/</v>
       </c>
       <c r="AC17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">    - xform/i8/i̍/</v>
       </c>
       <c r="AD17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/i9/i̋/</v>
       </c>
       <c r="AE17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v xml:space="preserve">    - xform/i0/i̊/</v>
       </c>
     </row>
@@ -3327,43 +3327,43 @@
         <v>ů</v>
       </c>
       <c r="V18" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/u1/u/</v>
+      </c>
+      <c r="W18" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/u2/ú/</v>
+      </c>
+      <c r="X18" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/u3/ù/</v>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/u4/u/</v>
+      </c>
+      <c r="Z18" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/u5/û/</v>
+      </c>
+      <c r="AA18" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/u6/ú/</v>
+      </c>
+      <c r="AB18" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/u7/ū/</v>
+      </c>
+      <c r="AC18" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    - xform/u8/u̍/</v>
+      </c>
+      <c r="AD18" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/u9/ű/</v>
+      </c>
+      <c r="AE18" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/u1/u/</v>
-      </c>
-      <c r="W18" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/u2/ú/</v>
-      </c>
-      <c r="X18" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/u3/ù/</v>
-      </c>
-      <c r="Y18" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/u4/u/</v>
-      </c>
-      <c r="Z18" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/u5/û/</v>
-      </c>
-      <c r="AA18" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/u6/ú/</v>
-      </c>
-      <c r="AB18" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    - xform/u7/ū/</v>
-      </c>
-      <c r="AC18" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/u8/u̍/</v>
-      </c>
-      <c r="AD18" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    - xform/u9/ű/</v>
-      </c>
-      <c r="AE18" t="str">
-        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/u0/ů/</v>
       </c>
     </row>
@@ -3412,43 +3412,43 @@
         <v>e̊</v>
       </c>
       <c r="V19" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/e1/e/</v>
+      </c>
+      <c r="W19" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/e2/é/</v>
+      </c>
+      <c r="X19" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/e3/è/</v>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/e4/e/</v>
+      </c>
+      <c r="Z19" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/e5/ê/</v>
+      </c>
+      <c r="AA19" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/e6/é/</v>
+      </c>
+      <c r="AB19" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/e7/ē/</v>
+      </c>
+      <c r="AC19" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    - xform/e8/e̍/</v>
+      </c>
+      <c r="AD19" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/e9/e̋/</v>
+      </c>
+      <c r="AE19" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/e1/e/</v>
-      </c>
-      <c r="W19" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/e2/é/</v>
-      </c>
-      <c r="X19" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/e3/è/</v>
-      </c>
-      <c r="Y19" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/e4/e/</v>
-      </c>
-      <c r="Z19" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/e5/ê/</v>
-      </c>
-      <c r="AA19" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/e6/é/</v>
-      </c>
-      <c r="AB19" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    - xform/e7/ē/</v>
-      </c>
-      <c r="AC19" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/e8/e̍/</v>
-      </c>
-      <c r="AD19" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    - xform/e9/e̋/</v>
-      </c>
-      <c r="AE19" t="str">
-        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/e0/e̊/</v>
       </c>
     </row>
@@ -3497,43 +3497,43 @@
         <v>o̊</v>
       </c>
       <c r="V20" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/o1/o/</v>
+      </c>
+      <c r="W20" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/o2/ó/</v>
+      </c>
+      <c r="X20" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/o3/ò/</v>
+      </c>
+      <c r="Y20" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/o4/o/</v>
+      </c>
+      <c r="Z20" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/o5/ô/</v>
+      </c>
+      <c r="AA20" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/o6/ó/</v>
+      </c>
+      <c r="AB20" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/o7/ō/</v>
+      </c>
+      <c r="AC20" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    - xform/o8/o̍/</v>
+      </c>
+      <c r="AD20" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/o9/ő/</v>
+      </c>
+      <c r="AE20" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/o1/o/</v>
-      </c>
-      <c r="W20" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/o2/ó/</v>
-      </c>
-      <c r="X20" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/o3/ò/</v>
-      </c>
-      <c r="Y20" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/o4/o/</v>
-      </c>
-      <c r="Z20" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/o5/ô/</v>
-      </c>
-      <c r="AA20" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/o6/ó/</v>
-      </c>
-      <c r="AB20" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    - xform/o7/ō/</v>
-      </c>
-      <c r="AC20" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/o8/o̍/</v>
-      </c>
-      <c r="AD20" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    - xform/o9/ő/</v>
-      </c>
-      <c r="AE20" t="str">
-        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/o0/o̊/</v>
       </c>
     </row>
@@ -3582,43 +3582,43 @@
         <v>m̊</v>
       </c>
       <c r="V21" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/m1/m/</v>
+      </c>
+      <c r="W21" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/m2/ḿ/</v>
+      </c>
+      <c r="X21" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/m3/m̀/</v>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/m4/m/</v>
+      </c>
+      <c r="Z21" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/m5/m̂/</v>
+      </c>
+      <c r="AA21" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/m6/ḿ/</v>
+      </c>
+      <c r="AB21" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/m7/m̄/</v>
+      </c>
+      <c r="AC21" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    - xform/m8/m̍/</v>
+      </c>
+      <c r="AD21" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/m9/m̋/</v>
+      </c>
+      <c r="AE21" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/m1/m/</v>
-      </c>
-      <c r="W21" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/m2/ḿ/</v>
-      </c>
-      <c r="X21" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/m3/m̀/</v>
-      </c>
-      <c r="Y21" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/m4/m/</v>
-      </c>
-      <c r="Z21" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/m5/m̂/</v>
-      </c>
-      <c r="AA21" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/m6/ḿ/</v>
-      </c>
-      <c r="AB21" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    - xform/m7/m̄/</v>
-      </c>
-      <c r="AC21" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/m8/m̍/</v>
-      </c>
-      <c r="AD21" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    - xform/m9/m̋/</v>
-      </c>
-      <c r="AE21" t="str">
-        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/m0/m̊/</v>
       </c>
     </row>
@@ -3667,43 +3667,43 @@
         <v>n̊</v>
       </c>
       <c r="V22" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/n1/n/</v>
+      </c>
+      <c r="W22" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/n2/ń/</v>
+      </c>
+      <c r="X22" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/n3/ǹ/</v>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/n4/n/</v>
+      </c>
+      <c r="Z22" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/n5/n̂/</v>
+      </c>
+      <c r="AA22" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">    - xform/n6/ń/</v>
+      </c>
+      <c r="AB22" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">    - xform/n7/n̄/</v>
+      </c>
+      <c r="AC22" t="str">
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">    - xform/n8/n̍/</v>
+      </c>
+      <c r="AD22" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/n9/n̋/</v>
+      </c>
+      <c r="AE22" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    - xform/n1/n/</v>
-      </c>
-      <c r="W22" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/n2/ń/</v>
-      </c>
-      <c r="X22" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/n3/ǹ/</v>
-      </c>
-      <c r="Y22" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/n4/n/</v>
-      </c>
-      <c r="Z22" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/n5/n̂/</v>
-      </c>
-      <c r="AA22" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    - xform/n6/ń/</v>
-      </c>
-      <c r="AB22" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    - xform/n7/n̄/</v>
-      </c>
-      <c r="AC22" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    - xform/n8/n̍/</v>
-      </c>
-      <c r="AD22" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    - xform/n9/n̋/</v>
-      </c>
-      <c r="AE22" t="str">
-        <f t="shared" si="8"/>
         <v xml:space="preserve">    - xform/n0/n̊/</v>
       </c>
     </row>
